--- a/uploads/ids.xlsx
+++ b/uploads/ids.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Development\App\Asset-Annotation-Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanvi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758AC756-B5C8-4F04-98A6-0ABBA3DDD34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F92527-A209-4372-AFF2-522294565789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23040" yWindow="156" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -368,10 +368,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -382,40 +385,239 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1010001</v>
+        <v>120101</v>
       </c>
       <c r="B2">
+        <v>147.26840625</v>
+      </c>
+      <c r="C2">
+        <v>117.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>120102</v>
+      </c>
+      <c r="B3">
+        <v>147.26840625</v>
+      </c>
+      <c r="C3">
+        <v>141.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>120103</v>
+      </c>
+      <c r="B4">
+        <v>211.27640625000001</v>
+      </c>
+      <c r="C4">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>120104</v>
+      </c>
+      <c r="B5">
+        <v>266.28328125000002</v>
+      </c>
+      <c r="C5">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>120105</v>
+      </c>
+      <c r="B6">
+        <v>317.28965625000001</v>
+      </c>
+      <c r="C6">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>120106</v>
+      </c>
+      <c r="B7">
+        <v>368.29603125</v>
+      </c>
+      <c r="C7">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>120107</v>
+      </c>
+      <c r="B8">
+        <v>426.30328125</v>
+      </c>
+      <c r="C8">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>120108</v>
+      </c>
+      <c r="B9">
+        <v>485.310656249999</v>
+      </c>
+      <c r="C9">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>120109</v>
+      </c>
+      <c r="B10">
+        <v>547.31840624999995</v>
+      </c>
+      <c r="C10">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>120110</v>
+      </c>
+      <c r="B11">
+        <v>619.32740624999997</v>
+      </c>
+      <c r="C11">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>120111</v>
+      </c>
+      <c r="B12">
+        <v>690.33628124999996</v>
+      </c>
+      <c r="C12">
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>120112</v>
+      </c>
+      <c r="B13">
+        <v>659.33240624999996</v>
+      </c>
+      <c r="C13">
+        <v>155.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>120113</v>
+      </c>
+      <c r="B14">
+        <v>759.34490625000001</v>
+      </c>
+      <c r="C14">
+        <v>116.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>120114</v>
+      </c>
+      <c r="B15">
+        <v>659.33240624999996</v>
+      </c>
+      <c r="C15">
+        <v>182.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>120115</v>
+      </c>
+      <c r="B16">
+        <v>758.34478124999998</v>
+      </c>
+      <c r="C16">
+        <v>164.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>120116</v>
+      </c>
+      <c r="B17">
+        <v>663.33290624999995</v>
+      </c>
+      <c r="C17">
+        <v>213.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>120117</v>
+      </c>
+      <c r="B18">
+        <v>638.32978125</v>
+      </c>
+      <c r="C18">
+        <v>212.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>120118</v>
+      </c>
+      <c r="B19">
         <v>100</v>
       </c>
-      <c r="C2">
+      <c r="C19">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1010002</v>
-      </c>
-      <c r="B3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>120119</v>
+      </c>
+      <c r="B20">
+        <v>110</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>120120</v>
+      </c>
+      <c r="B21">
         <v>120</v>
       </c>
-      <c r="C3">
+      <c r="C21">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1010003</v>
-      </c>
-      <c r="B4">
-        <v>140</v>
-      </c>
-      <c r="C4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>120121</v>
+      </c>
+      <c r="B22">
+        <v>130</v>
+      </c>
+      <c r="C22">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>